--- a/data/dimensions/dim_departamentos.xlsx
+++ b/data/dimensions/dim_departamentos.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>codigo_departamento</t>
   </si>
@@ -27,100 +27,13 @@
     <t>nombre</t>
   </si>
   <si>
-    <t>Antioquia</t>
-  </si>
-  <si>
-    <t>Caldas</t>
-  </si>
-  <si>
-    <t>Cauca</t>
-  </si>
-  <si>
     <t>Cesar</t>
-  </si>
-  <si>
-    <t>Cundinamarca</t>
-  </si>
-  <si>
-    <t>Guaviare</t>
   </si>
   <si>
     <t>La Guajira</t>
   </si>
   <si>
     <t>Magdalena</t>
-  </si>
-  <si>
-    <t>Meta</t>
-  </si>
-  <si>
-    <t>Norte de Santander</t>
-  </si>
-  <si>
-    <t>Risaralda</t>
-  </si>
-  <si>
-    <t>Santander</t>
-  </si>
-  <si>
-    <t>Sucre</t>
-  </si>
-  <si>
-    <t>Tolima</t>
-  </si>
-  <si>
-    <t>Valle del Cauca</t>
-  </si>
-  <si>
-    <t>Arauca</t>
-  </si>
-  <si>
-    <t>Casanare</t>
-  </si>
-  <si>
-    <t>Putumayo</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Vichada</t>
-  </si>
-  <si>
-    <t>Atlántico</t>
-  </si>
-  <si>
-    <t>Bogotá D.C.</t>
-  </si>
-  <si>
-    <t>Boyacá</t>
-  </si>
-  <si>
-    <t>Caquetá</t>
-  </si>
-  <si>
-    <t>Bolívar</t>
-  </si>
-  <si>
-    <t>Guainía</t>
-  </si>
-  <si>
-    <t>Quindío</t>
-  </si>
-  <si>
-    <t>Córdoba</t>
-  </si>
-  <si>
-    <t>Chocó</t>
-  </si>
-  <si>
-    <t>Nariño</t>
-  </si>
-  <si>
-    <t>Archipiélago de San Andrés Providencia y Santa Catalina</t>
-  </si>
-  <si>
-    <t>Vaupés</t>
   </si>
 </sst>
 </file>
@@ -927,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.140625" bestFit="1" customWidth="1"/>
@@ -943,7 +856,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -951,250 +864,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>27</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>41</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>44</v>
-      </c>
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>50</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>52</v>
-      </c>
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>55</v>
-      </c>
-      <c r="B20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>63</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>66</v>
-      </c>
-      <c r="B22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>68</v>
-      </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>70</v>
-      </c>
-      <c r="B24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>73</v>
-      </c>
-      <c r="B25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>76</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>81</v>
-      </c>
-      <c r="B27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>85</v>
-      </c>
-      <c r="B28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>86</v>
-      </c>
-      <c r="B29" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>88</v>
-      </c>
-      <c r="B30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>91</v>
-      </c>
-      <c r="B31" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>94</v>
-      </c>
-      <c r="B32" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>95</v>
-      </c>
-      <c r="B33" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
